--- a/artfynd/A 39293-2024 artfynd.xlsx
+++ b/artfynd/A 39293-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120836326</v>
       </c>
       <c r="B2" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>120834043</v>
       </c>
       <c r="B3" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120872400</v>
+        <v>120855258</v>
       </c>
       <c r="B4" t="n">
-        <v>91083</v>
+        <v>98001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,40 +940,47 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4217</v>
+        <v>223597</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>SO Svarttjärn, Vstm</t>
+          <t>Svarttjärnen, SO om, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535897</v>
+        <v>535701</v>
       </c>
       <c r="R4" t="n">
-        <v>6609937</v>
+        <v>6610181</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,29 +1018,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrskog, fuktig</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Bengt Stridh</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bertil Svensson, Lars Bohlin, Bengt Stridh, Josefin Kjellberg, Dennis JP Nyström</t>
+          <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg, Lars Bohlin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120855258</v>
+        <v>120872400</v>
       </c>
       <c r="B5" t="n">
-        <v>97991</v>
+        <v>91093</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,47 +1057,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223597</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svarttjärnen, SO om, Vstm</t>
+          <t>SO Svarttjärn, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535701</v>
+        <v>535897</v>
       </c>
       <c r="R5" t="n">
-        <v>6610181</v>
+        <v>6609937</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,23 +1128,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrskog, fuktig</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bengt Stridh</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg, Lars Bohlin</t>
+          <t>Bertil Svensson, Lars Bohlin, Bengt Stridh, Josefin Kjellberg, Dennis JP Nyström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1262,7 +1262,7 @@
         <v>120854673</v>
       </c>
       <c r="B7" t="n">
-        <v>91083</v>
+        <v>91093</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>120875031</v>
       </c>
       <c r="B8" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>120875026</v>
       </c>
       <c r="B9" t="n">
-        <v>105176</v>
+        <v>105186</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>120875029</v>
       </c>
       <c r="B10" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>120844577</v>
       </c>
       <c r="B11" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120844485</v>
+        <v>120875022</v>
       </c>
       <c r="B12" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1883,17 +1883,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svarttjärnen, öster om, Vstm</t>
+          <t>SO Svarttjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535716</v>
+        <v>535419</v>
       </c>
       <c r="R12" t="n">
-        <v>6610354</v>
+        <v>6609645</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1935,30 +1935,25 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Stridh</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg, Lars Bohlin, Bertil Svensson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120875022</v>
+        <v>120844485</v>
       </c>
       <c r="B13" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1990,7 +1985,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2002,17 +1997,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>SO Svarttjärnen, Vstm</t>
+          <t>Svarttjärnen, öster om, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535419</v>
+        <v>535716</v>
       </c>
       <c r="R13" t="n">
-        <v>6609645</v>
+        <v>6610354</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2054,15 +2049,20 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Bengt Stridh</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg, Lars Bohlin, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 39293-2024 artfynd.xlsx
+++ b/artfynd/A 39293-2024 artfynd.xlsx
@@ -924,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120855258</v>
+        <v>120872400</v>
       </c>
       <c r="B4" t="n">
-        <v>98001</v>
+        <v>91093</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,47 +940,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223597</v>
+        <v>4217</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svarttjärnen, SO om, Vstm</t>
+          <t>SO Svarttjärn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535701</v>
+        <v>535897</v>
       </c>
       <c r="R4" t="n">
-        <v>6610181</v>
+        <v>6609937</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,33 +1011,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrskog, fuktig</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bengt Stridh</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg, Lars Bohlin</t>
+          <t>Bertil Svensson, Lars Bohlin, Bengt Stridh, Josefin Kjellberg, Dennis JP Nyström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120872400</v>
+        <v>120855258</v>
       </c>
       <c r="B5" t="n">
-        <v>91093</v>
+        <v>98001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,40 +1046,47 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>223597</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SO Svarttjärn, Vstm</t>
+          <t>Svarttjärnen, SO om, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535897</v>
+        <v>535701</v>
       </c>
       <c r="R5" t="n">
-        <v>6609937</v>
+        <v>6610181</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,19 +1124,23 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrskog, fuktig</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Bengt Stridh</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bertil Svensson, Lars Bohlin, Bengt Stridh, Josefin Kjellberg, Dennis JP Nyström</t>
+          <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg, Lars Bohlin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bertil Svensson, Lars Bohlin, Bengt Stridh, Josefin Kjellberg, Dennis JP Nyström</t>
+          <t>Bertil Svensson, Dennis JP Nyström, Josefin Kjellberg, Bengt Stridh, Lars Bohlin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1717,7 +1717,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120844577</v>
+        <v>120875022</v>
       </c>
       <c r="B11" t="n">
         <v>92008</v>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1764,17 +1764,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svarttjärnen, SO om, Vstm</t>
+          <t>SO Svarttjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535831</v>
+        <v>535419</v>
       </c>
       <c r="R11" t="n">
-        <v>6609952</v>
+        <v>6609645</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1816,27 +1816,22 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Stridh</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg, Lars Bohlin</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120875022</v>
+        <v>120844577</v>
       </c>
       <c r="B12" t="n">
         <v>92008</v>
@@ -1871,7 +1866,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1883,17 +1878,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>SO Svarttjärnen, Vstm</t>
+          <t>Svarttjärnen, SO om, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535419</v>
+        <v>535831</v>
       </c>
       <c r="R12" t="n">
-        <v>6609645</v>
+        <v>6609952</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1935,15 +1930,20 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Bengt Stridh</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg, Lars Bohlin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg, Lars Bohlin, Bertil Svensson</t>
+          <t>Bertil Svensson, Lars Bohlin, Josefin Kjellberg, Dennis JP Nyström, Bengt Stridh</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 39293-2024 artfynd.xlsx
+++ b/artfynd/A 39293-2024 artfynd.xlsx
@@ -1717,10 +1717,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120875022</v>
+        <v>120844577</v>
       </c>
       <c r="B11" t="n">
-        <v>92008</v>
+        <v>92020</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1764,17 +1764,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>SO Svarttjärnen, Vstm</t>
+          <t>Svarttjärnen, SO om, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535419</v>
+        <v>535831</v>
       </c>
       <c r="R11" t="n">
-        <v>6609645</v>
+        <v>6609952</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1816,25 +1816,30 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Bengt Stridh</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg, Lars Bohlin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120844577</v>
+        <v>120875022</v>
       </c>
       <c r="B12" t="n">
-        <v>92008</v>
+        <v>92020</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,7 +1871,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1878,17 +1883,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svarttjärnen, SO om, Vstm</t>
+          <t>SO Svarttjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535831</v>
+        <v>535419</v>
       </c>
       <c r="R12" t="n">
-        <v>6609952</v>
+        <v>6609645</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1930,20 +1935,15 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bengt Stridh</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg, Lars Bohlin</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1953,7 +1953,7 @@
         <v>120844485</v>
       </c>
       <c r="B13" t="n">
-        <v>92008</v>
+        <v>92020</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bertil Svensson, Lars Bohlin, Josefin Kjellberg, Dennis JP Nyström, Bengt Stridh</t>
+          <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg, Lars Bohlin, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 39293-2024 artfynd.xlsx
+++ b/artfynd/A 39293-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120836326</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>120834043</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 39293-2024 artfynd.xlsx
+++ b/artfynd/A 39293-2024 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>100049</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -771,11 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -819,11 +809,6 @@
       </c>
       <c r="E3" t="n">
         <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 39293-2024 artfynd.xlsx
+++ b/artfynd/A 39293-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120836326</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>100049</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -766,6 +771,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -795,7 +805,7 @@
         <v>120834043</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,6 +819,11 @@
       </c>
       <c r="E3" t="n">
         <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
